--- a/underwriting/tests/fixtures/sample-grid.xlsx
+++ b/underwriting/tests/fixtures/sample-grid.xlsx
@@ -509,7 +509,6 @@
           <t>Eliquis</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -529,7 +528,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>See notes</t>
+          <t>Ask Bob</t>
         </is>
       </c>
     </row>

--- a/underwriting/tests/fixtures/sample-grid.xlsx
+++ b/underwriting/tests/fixtures/sample-grid.xlsx
@@ -535,7 +535,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gout</t>
+          <t>Zebra Fever</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
